--- a/security-tests/ReconAI_Security_Audit_Report_300_TestCases.xlsx
+++ b/security-tests/ReconAI_Security_Audit_Report_300_TestCases.xlsx
@@ -17,7 +17,7 @@
     <t>RECONAI SURGICAL PLATFORM - SECURITY SAST AUDIT REPORT</t>
   </si>
   <si>
-    <t>Review Mode: Static Application Security Testing (SAST) | Date: 11/8/2026</t>
+    <t>Review Mode: Static Application Security Testing (SAST) | Date: 14/8/2026</t>
   </si>
   <si>
     <t>Metric Name</t>
@@ -143,7 +143,7 @@
     <t>Static Analysis Engine</t>
   </si>
   <si>
-    <t>2026-08-11T03:44:15.533Z</t>
+    <t>2026-08-14T04:04:06.293Z</t>
   </si>
   <si>
     <t>TC-SEC-002</t>
@@ -3023,7 +3023,7 @@
         <v>40</v>
       </c>
       <c r="K2" s="8">
-        <v>14</v>
+        <v>54</v>
       </c>
       <c r="L2" s="8" t="s">
         <v>41</v>
@@ -3064,7 +3064,7 @@
         <v>47</v>
       </c>
       <c r="K3" s="8">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="L3" s="8" t="s">
         <v>41</v>
@@ -3105,7 +3105,7 @@
         <v>52</v>
       </c>
       <c r="K4" s="8">
-        <v>57</v>
+        <v>21</v>
       </c>
       <c r="L4" s="8" t="s">
         <v>41</v>
@@ -3146,7 +3146,7 @@
         <v>56</v>
       </c>
       <c r="K5" s="8">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="L5" s="8" t="s">
         <v>41</v>
@@ -3187,7 +3187,7 @@
         <v>60</v>
       </c>
       <c r="K6" s="8">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="L6" s="8" t="s">
         <v>41</v>
@@ -3228,7 +3228,7 @@
         <v>40</v>
       </c>
       <c r="K7" s="8">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="L7" s="8" t="s">
         <v>41</v>
@@ -3269,7 +3269,7 @@
         <v>47</v>
       </c>
       <c r="K8" s="8">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="L8" s="8" t="s">
         <v>41</v>
@@ -3351,7 +3351,7 @@
         <v>56</v>
       </c>
       <c r="K10" s="8">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="L10" s="8" t="s">
         <v>41</v>
@@ -3392,7 +3392,7 @@
         <v>60</v>
       </c>
       <c r="K11" s="8">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="L11" s="8" t="s">
         <v>41</v>
@@ -3433,7 +3433,7 @@
         <v>40</v>
       </c>
       <c r="K12" s="8">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="L12" s="8" t="s">
         <v>41</v>
@@ -3474,7 +3474,7 @@
         <v>47</v>
       </c>
       <c r="K13" s="8">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="L13" s="8" t="s">
         <v>41</v>
@@ -3515,7 +3515,7 @@
         <v>52</v>
       </c>
       <c r="K14" s="8">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="L14" s="8" t="s">
         <v>41</v>
@@ -3556,7 +3556,7 @@
         <v>56</v>
       </c>
       <c r="K15" s="8">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="L15" s="8" t="s">
         <v>41</v>
@@ -3597,7 +3597,7 @@
         <v>60</v>
       </c>
       <c r="K16" s="8">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="L16" s="8" t="s">
         <v>41</v>
@@ -3638,7 +3638,7 @@
         <v>40</v>
       </c>
       <c r="K17" s="8">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="L17" s="8" t="s">
         <v>41</v>
@@ -3679,7 +3679,7 @@
         <v>47</v>
       </c>
       <c r="K18" s="8">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="L18" s="8" t="s">
         <v>41</v>
@@ -3720,7 +3720,7 @@
         <v>52</v>
       </c>
       <c r="K19" s="8">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="L19" s="8" t="s">
         <v>41</v>
@@ -3761,7 +3761,7 @@
         <v>56</v>
       </c>
       <c r="K20" s="8">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="L20" s="8" t="s">
         <v>41</v>
@@ -3802,7 +3802,7 @@
         <v>60</v>
       </c>
       <c r="K21" s="8">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="L21" s="8" t="s">
         <v>41</v>
@@ -3843,7 +3843,7 @@
         <v>40</v>
       </c>
       <c r="K22" s="8">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="L22" s="8" t="s">
         <v>41</v>
@@ -3884,7 +3884,7 @@
         <v>47</v>
       </c>
       <c r="K23" s="8">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="L23" s="8" t="s">
         <v>41</v>
@@ -3966,7 +3966,7 @@
         <v>56</v>
       </c>
       <c r="K25" s="8">
-        <v>44</v>
+        <v>19</v>
       </c>
       <c r="L25" s="8" t="s">
         <v>41</v>
@@ -4007,7 +4007,7 @@
         <v>60</v>
       </c>
       <c r="K26" s="8">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="L26" s="8" t="s">
         <v>41</v>
@@ -4048,7 +4048,7 @@
         <v>40</v>
       </c>
       <c r="K27" s="8">
-        <v>34</v>
+        <v>59</v>
       </c>
       <c r="L27" s="8" t="s">
         <v>41</v>
@@ -4089,7 +4089,7 @@
         <v>47</v>
       </c>
       <c r="K28" s="8">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L28" s="8" t="s">
         <v>41</v>
@@ -4130,7 +4130,7 @@
         <v>52</v>
       </c>
       <c r="K29" s="8">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="L29" s="8" t="s">
         <v>41</v>
@@ -4171,7 +4171,7 @@
         <v>56</v>
       </c>
       <c r="K30" s="8">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="L30" s="8" t="s">
         <v>41</v>
@@ -4212,7 +4212,7 @@
         <v>60</v>
       </c>
       <c r="K31" s="8">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="L31" s="8" t="s">
         <v>41</v>
@@ -4253,7 +4253,7 @@
         <v>40</v>
       </c>
       <c r="K32" s="8">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="L32" s="8" t="s">
         <v>41</v>
@@ -4294,7 +4294,7 @@
         <v>47</v>
       </c>
       <c r="K33" s="8">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="L33" s="8" t="s">
         <v>41</v>
@@ -4335,7 +4335,7 @@
         <v>52</v>
       </c>
       <c r="K34" s="8">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="L34" s="8" t="s">
         <v>41</v>
@@ -4376,7 +4376,7 @@
         <v>56</v>
       </c>
       <c r="K35" s="8">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="L35" s="8" t="s">
         <v>41</v>
@@ -4417,7 +4417,7 @@
         <v>60</v>
       </c>
       <c r="K36" s="8">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="L36" s="8" t="s">
         <v>41</v>
@@ -4458,7 +4458,7 @@
         <v>40</v>
       </c>
       <c r="K37" s="8">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="L37" s="8" t="s">
         <v>41</v>
@@ -4499,7 +4499,7 @@
         <v>47</v>
       </c>
       <c r="K38" s="8">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="L38" s="8" t="s">
         <v>41</v>
@@ -4540,7 +4540,7 @@
         <v>52</v>
       </c>
       <c r="K39" s="8">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="L39" s="8" t="s">
         <v>41</v>
@@ -4581,7 +4581,7 @@
         <v>56</v>
       </c>
       <c r="K40" s="8">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="L40" s="8" t="s">
         <v>41</v>
@@ -4622,7 +4622,7 @@
         <v>60</v>
       </c>
       <c r="K41" s="8">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="L41" s="8" t="s">
         <v>41</v>
@@ -4663,7 +4663,7 @@
         <v>40</v>
       </c>
       <c r="K42" s="8">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="L42" s="8" t="s">
         <v>41</v>
@@ -4704,7 +4704,7 @@
         <v>47</v>
       </c>
       <c r="K43" s="8">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="L43" s="8" t="s">
         <v>41</v>
@@ -4745,7 +4745,7 @@
         <v>52</v>
       </c>
       <c r="K44" s="8">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="L44" s="8" t="s">
         <v>41</v>
@@ -4786,7 +4786,7 @@
         <v>56</v>
       </c>
       <c r="K45" s="8">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="L45" s="8" t="s">
         <v>41</v>
@@ -4827,7 +4827,7 @@
         <v>60</v>
       </c>
       <c r="K46" s="8">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="L46" s="8" t="s">
         <v>41</v>
@@ -4868,7 +4868,7 @@
         <v>40</v>
       </c>
       <c r="K47" s="8">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="L47" s="8" t="s">
         <v>41</v>
@@ -4909,7 +4909,7 @@
         <v>47</v>
       </c>
       <c r="K48" s="8">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="L48" s="8" t="s">
         <v>41</v>
@@ -4950,7 +4950,7 @@
         <v>52</v>
       </c>
       <c r="K49" s="8">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="L49" s="8" t="s">
         <v>41</v>
@@ -4991,7 +4991,7 @@
         <v>56</v>
       </c>
       <c r="K50" s="8">
-        <v>58</v>
+        <v>21</v>
       </c>
       <c r="L50" s="8" t="s">
         <v>41</v>
@@ -5032,7 +5032,7 @@
         <v>60</v>
       </c>
       <c r="K51" s="8">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="L51" s="8" t="s">
         <v>41</v>
@@ -5073,7 +5073,7 @@
         <v>40</v>
       </c>
       <c r="K52" s="8">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="L52" s="8" t="s">
         <v>41</v>
@@ -5114,7 +5114,7 @@
         <v>47</v>
       </c>
       <c r="K53" s="8">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="L53" s="8" t="s">
         <v>41</v>
@@ -5155,7 +5155,7 @@
         <v>52</v>
       </c>
       <c r="K54" s="8">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L54" s="8" t="s">
         <v>41</v>
@@ -5196,7 +5196,7 @@
         <v>56</v>
       </c>
       <c r="K55" s="8">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L55" s="8" t="s">
         <v>41</v>
@@ -5237,7 +5237,7 @@
         <v>60</v>
       </c>
       <c r="K56" s="8">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="L56" s="8" t="s">
         <v>41</v>
@@ -5278,7 +5278,7 @@
         <v>40</v>
       </c>
       <c r="K57" s="8">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="L57" s="8" t="s">
         <v>41</v>
@@ -5319,7 +5319,7 @@
         <v>47</v>
       </c>
       <c r="K58" s="8">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L58" s="8" t="s">
         <v>41</v>
@@ -5360,7 +5360,7 @@
         <v>52</v>
       </c>
       <c r="K59" s="8">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="L59" s="8" t="s">
         <v>41</v>
@@ -5401,7 +5401,7 @@
         <v>56</v>
       </c>
       <c r="K60" s="8">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="L60" s="8" t="s">
         <v>41</v>
@@ -5442,7 +5442,7 @@
         <v>60</v>
       </c>
       <c r="K61" s="8">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="L61" s="8" t="s">
         <v>41</v>
@@ -5483,7 +5483,7 @@
         <v>40</v>
       </c>
       <c r="K62" s="8">
-        <v>15</v>
+        <v>51</v>
       </c>
       <c r="L62" s="8" t="s">
         <v>41</v>
@@ -5524,7 +5524,7 @@
         <v>47</v>
       </c>
       <c r="K63" s="8">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="L63" s="8" t="s">
         <v>41</v>
@@ -5565,7 +5565,7 @@
         <v>52</v>
       </c>
       <c r="K64" s="8">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="L64" s="8" t="s">
         <v>41</v>
@@ -5606,7 +5606,7 @@
         <v>56</v>
       </c>
       <c r="K65" s="8">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="L65" s="8" t="s">
         <v>41</v>
@@ -5647,7 +5647,7 @@
         <v>60</v>
       </c>
       <c r="K66" s="8">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="L66" s="8" t="s">
         <v>41</v>
@@ -5688,7 +5688,7 @@
         <v>40</v>
       </c>
       <c r="K67" s="8">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="L67" s="8" t="s">
         <v>41</v>
@@ -5729,7 +5729,7 @@
         <v>47</v>
       </c>
       <c r="K68" s="8">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="L68" s="8" t="s">
         <v>41</v>
@@ -5770,7 +5770,7 @@
         <v>52</v>
       </c>
       <c r="K69" s="8">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="L69" s="8" t="s">
         <v>41</v>
@@ -5811,7 +5811,7 @@
         <v>56</v>
       </c>
       <c r="K70" s="8">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="L70" s="8" t="s">
         <v>41</v>
@@ -5852,7 +5852,7 @@
         <v>60</v>
       </c>
       <c r="K71" s="8">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="L71" s="8" t="s">
         <v>41</v>
@@ -5893,7 +5893,7 @@
         <v>40</v>
       </c>
       <c r="K72" s="8">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="L72" s="8" t="s">
         <v>41</v>
@@ -5934,7 +5934,7 @@
         <v>47</v>
       </c>
       <c r="K73" s="8">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="L73" s="8" t="s">
         <v>41</v>
@@ -6016,7 +6016,7 @@
         <v>56</v>
       </c>
       <c r="K75" s="8">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="L75" s="8" t="s">
         <v>41</v>
@@ -6057,7 +6057,7 @@
         <v>60</v>
       </c>
       <c r="K76" s="8">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="L76" s="8" t="s">
         <v>41</v>
@@ -6098,7 +6098,7 @@
         <v>40</v>
       </c>
       <c r="K77" s="8">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="L77" s="8" t="s">
         <v>41</v>
@@ -6139,7 +6139,7 @@
         <v>47</v>
       </c>
       <c r="K78" s="8">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="L78" s="8" t="s">
         <v>41</v>
@@ -6180,7 +6180,7 @@
         <v>52</v>
       </c>
       <c r="K79" s="8">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L79" s="8" t="s">
         <v>41</v>
@@ -6221,7 +6221,7 @@
         <v>56</v>
       </c>
       <c r="K80" s="8">
-        <v>10</v>
+        <v>49</v>
       </c>
       <c r="L80" s="8" t="s">
         <v>41</v>
@@ -6262,7 +6262,7 @@
         <v>60</v>
       </c>
       <c r="K81" s="8">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="L81" s="8" t="s">
         <v>41</v>
@@ -6303,7 +6303,7 @@
         <v>40</v>
       </c>
       <c r="K82" s="8">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="L82" s="8" t="s">
         <v>41</v>
@@ -6344,7 +6344,7 @@
         <v>47</v>
       </c>
       <c r="K83" s="8">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="L83" s="8" t="s">
         <v>41</v>
@@ -6385,7 +6385,7 @@
         <v>52</v>
       </c>
       <c r="K84" s="8">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="L84" s="8" t="s">
         <v>41</v>
@@ -6426,7 +6426,7 @@
         <v>56</v>
       </c>
       <c r="K85" s="8">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="L85" s="8" t="s">
         <v>41</v>
@@ -6467,7 +6467,7 @@
         <v>60</v>
       </c>
       <c r="K86" s="8">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="L86" s="8" t="s">
         <v>41</v>
@@ -6508,7 +6508,7 @@
         <v>40</v>
       </c>
       <c r="K87" s="8">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="L87" s="8" t="s">
         <v>41</v>
@@ -6549,7 +6549,7 @@
         <v>47</v>
       </c>
       <c r="K88" s="8">
-        <v>21</v>
+        <v>51</v>
       </c>
       <c r="L88" s="8" t="s">
         <v>41</v>
@@ -6590,7 +6590,7 @@
         <v>52</v>
       </c>
       <c r="K89" s="8">
-        <v>10</v>
+        <v>54</v>
       </c>
       <c r="L89" s="8" t="s">
         <v>41</v>
@@ -6631,7 +6631,7 @@
         <v>56</v>
       </c>
       <c r="K90" s="8">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="L90" s="8" t="s">
         <v>41</v>
@@ -6672,7 +6672,7 @@
         <v>60</v>
       </c>
       <c r="K91" s="8">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="L91" s="8" t="s">
         <v>41</v>
@@ -6713,7 +6713,7 @@
         <v>40</v>
       </c>
       <c r="K92" s="8">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="L92" s="8" t="s">
         <v>41</v>
@@ -6754,7 +6754,7 @@
         <v>47</v>
       </c>
       <c r="K93" s="8">
-        <v>14</v>
+        <v>52</v>
       </c>
       <c r="L93" s="8" t="s">
         <v>41</v>
@@ -6795,7 +6795,7 @@
         <v>52</v>
       </c>
       <c r="K94" s="8">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="L94" s="8" t="s">
         <v>41</v>
@@ -6836,7 +6836,7 @@
         <v>56</v>
       </c>
       <c r="K95" s="8">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="L95" s="8" t="s">
         <v>41</v>
@@ -6877,7 +6877,7 @@
         <v>60</v>
       </c>
       <c r="K96" s="8">
-        <v>10</v>
+        <v>58</v>
       </c>
       <c r="L96" s="8" t="s">
         <v>41</v>
@@ -6918,7 +6918,7 @@
         <v>40</v>
       </c>
       <c r="K97" s="8">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="L97" s="8" t="s">
         <v>41</v>
@@ -6959,7 +6959,7 @@
         <v>47</v>
       </c>
       <c r="K98" s="8">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="L98" s="8" t="s">
         <v>41</v>
@@ -7000,7 +7000,7 @@
         <v>52</v>
       </c>
       <c r="K99" s="8">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="L99" s="8" t="s">
         <v>41</v>
@@ -7041,7 +7041,7 @@
         <v>56</v>
       </c>
       <c r="K100" s="8">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="L100" s="8" t="s">
         <v>41</v>
@@ -7082,7 +7082,7 @@
         <v>60</v>
       </c>
       <c r="K101" s="8">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="L101" s="8" t="s">
         <v>41</v>
@@ -7123,7 +7123,7 @@
         <v>40</v>
       </c>
       <c r="K102" s="8">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="L102" s="8" t="s">
         <v>41</v>
@@ -7164,7 +7164,7 @@
         <v>47</v>
       </c>
       <c r="K103" s="8">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="L103" s="8" t="s">
         <v>41</v>
@@ -7205,7 +7205,7 @@
         <v>52</v>
       </c>
       <c r="K104" s="8">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="L104" s="8" t="s">
         <v>41</v>
@@ -7246,7 +7246,7 @@
         <v>56</v>
       </c>
       <c r="K105" s="8">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="L105" s="8" t="s">
         <v>41</v>
@@ -7287,7 +7287,7 @@
         <v>60</v>
       </c>
       <c r="K106" s="8">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="L106" s="8" t="s">
         <v>41</v>
@@ -7328,7 +7328,7 @@
         <v>40</v>
       </c>
       <c r="K107" s="8">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="L107" s="8" t="s">
         <v>41</v>
@@ -7369,7 +7369,7 @@
         <v>47</v>
       </c>
       <c r="K108" s="8">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="L108" s="8" t="s">
         <v>41</v>
@@ -7410,7 +7410,7 @@
         <v>52</v>
       </c>
       <c r="K109" s="8">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="L109" s="8" t="s">
         <v>41</v>
@@ -7451,7 +7451,7 @@
         <v>56</v>
       </c>
       <c r="K110" s="8">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="L110" s="8" t="s">
         <v>41</v>
@@ -7492,7 +7492,7 @@
         <v>60</v>
       </c>
       <c r="K111" s="8">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L111" s="8" t="s">
         <v>41</v>
@@ -7533,7 +7533,7 @@
         <v>40</v>
       </c>
       <c r="K112" s="8">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="L112" s="8" t="s">
         <v>41</v>
@@ -7574,7 +7574,7 @@
         <v>47</v>
       </c>
       <c r="K113" s="8">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="L113" s="8" t="s">
         <v>41</v>
@@ -7615,7 +7615,7 @@
         <v>52</v>
       </c>
       <c r="K114" s="8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L114" s="8" t="s">
         <v>41</v>
@@ -7656,7 +7656,7 @@
         <v>56</v>
       </c>
       <c r="K115" s="8">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="L115" s="8" t="s">
         <v>41</v>
@@ -7697,7 +7697,7 @@
         <v>60</v>
       </c>
       <c r="K116" s="8">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="L116" s="8" t="s">
         <v>41</v>
@@ -7779,7 +7779,7 @@
         <v>47</v>
       </c>
       <c r="K118" s="8">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="L118" s="8" t="s">
         <v>41</v>
@@ -7820,7 +7820,7 @@
         <v>52</v>
       </c>
       <c r="K119" s="8">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="L119" s="8" t="s">
         <v>41</v>
@@ -7861,7 +7861,7 @@
         <v>56</v>
       </c>
       <c r="K120" s="8">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="L120" s="8" t="s">
         <v>41</v>
@@ -7902,7 +7902,7 @@
         <v>60</v>
       </c>
       <c r="K121" s="8">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="L121" s="8" t="s">
         <v>41</v>
@@ -7943,7 +7943,7 @@
         <v>40</v>
       </c>
       <c r="K122" s="8">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="L122" s="8" t="s">
         <v>41</v>
@@ -7984,7 +7984,7 @@
         <v>47</v>
       </c>
       <c r="K123" s="8">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="L123" s="8" t="s">
         <v>41</v>
@@ -8025,7 +8025,7 @@
         <v>52</v>
       </c>
       <c r="K124" s="8">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="L124" s="8" t="s">
         <v>41</v>
@@ -8066,7 +8066,7 @@
         <v>56</v>
       </c>
       <c r="K125" s="8">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="L125" s="8" t="s">
         <v>41</v>
@@ -8107,7 +8107,7 @@
         <v>60</v>
       </c>
       <c r="K126" s="8">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="L126" s="8" t="s">
         <v>41</v>
@@ -8148,7 +8148,7 @@
         <v>40</v>
       </c>
       <c r="K127" s="8">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="L127" s="8" t="s">
         <v>41</v>
@@ -8189,7 +8189,7 @@
         <v>47</v>
       </c>
       <c r="K128" s="8">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="L128" s="8" t="s">
         <v>41</v>
@@ -8230,7 +8230,7 @@
         <v>52</v>
       </c>
       <c r="K129" s="8">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="L129" s="8" t="s">
         <v>41</v>
@@ -8271,7 +8271,7 @@
         <v>56</v>
       </c>
       <c r="K130" s="8">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="L130" s="8" t="s">
         <v>41</v>
@@ -8312,7 +8312,7 @@
         <v>60</v>
       </c>
       <c r="K131" s="8">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="L131" s="8" t="s">
         <v>41</v>
@@ -8353,7 +8353,7 @@
         <v>40</v>
       </c>
       <c r="K132" s="8">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="L132" s="8" t="s">
         <v>41</v>
@@ -8394,7 +8394,7 @@
         <v>47</v>
       </c>
       <c r="K133" s="8">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="L133" s="8" t="s">
         <v>41</v>
@@ -8435,7 +8435,7 @@
         <v>52</v>
       </c>
       <c r="K134" s="8">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="L134" s="8" t="s">
         <v>41</v>
@@ -8476,7 +8476,7 @@
         <v>56</v>
       </c>
       <c r="K135" s="8">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="L135" s="8" t="s">
         <v>41</v>
@@ -8517,7 +8517,7 @@
         <v>60</v>
       </c>
       <c r="K136" s="8">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="L136" s="8" t="s">
         <v>41</v>
@@ -8599,7 +8599,7 @@
         <v>47</v>
       </c>
       <c r="K138" s="8">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="L138" s="8" t="s">
         <v>41</v>
@@ -8640,7 +8640,7 @@
         <v>52</v>
       </c>
       <c r="K139" s="8">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="L139" s="8" t="s">
         <v>41</v>
@@ -8681,7 +8681,7 @@
         <v>56</v>
       </c>
       <c r="K140" s="8">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="L140" s="8" t="s">
         <v>41</v>
@@ -8722,7 +8722,7 @@
         <v>60</v>
       </c>
       <c r="K141" s="8">
-        <v>58</v>
+        <v>21</v>
       </c>
       <c r="L141" s="8" t="s">
         <v>41</v>
@@ -8763,7 +8763,7 @@
         <v>40</v>
       </c>
       <c r="K142" s="8">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="L142" s="8" t="s">
         <v>41</v>
@@ -8804,7 +8804,7 @@
         <v>47</v>
       </c>
       <c r="K143" s="8">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="L143" s="8" t="s">
         <v>41</v>
@@ -8845,7 +8845,7 @@
         <v>52</v>
       </c>
       <c r="K144" s="8">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="L144" s="8" t="s">
         <v>41</v>
@@ -8886,7 +8886,7 @@
         <v>56</v>
       </c>
       <c r="K145" s="8">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="L145" s="8" t="s">
         <v>41</v>
@@ -8927,7 +8927,7 @@
         <v>60</v>
       </c>
       <c r="K146" s="8">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="L146" s="8" t="s">
         <v>41</v>
@@ -8968,7 +8968,7 @@
         <v>40</v>
       </c>
       <c r="K147" s="8">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="L147" s="8" t="s">
         <v>41</v>
@@ -9009,7 +9009,7 @@
         <v>47</v>
       </c>
       <c r="K148" s="8">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="L148" s="8" t="s">
         <v>41</v>
@@ -9050,7 +9050,7 @@
         <v>52</v>
       </c>
       <c r="K149" s="8">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="L149" s="8" t="s">
         <v>41</v>
@@ -9091,7 +9091,7 @@
         <v>56</v>
       </c>
       <c r="K150" s="8">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="L150" s="8" t="s">
         <v>41</v>
@@ -9132,7 +9132,7 @@
         <v>60</v>
       </c>
       <c r="K151" s="8">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="L151" s="8" t="s">
         <v>41</v>
@@ -9173,7 +9173,7 @@
         <v>40</v>
       </c>
       <c r="K152" s="8">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="L152" s="8" t="s">
         <v>41</v>
@@ -9214,7 +9214,7 @@
         <v>47</v>
       </c>
       <c r="K153" s="8">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="L153" s="8" t="s">
         <v>41</v>
@@ -9255,7 +9255,7 @@
         <v>52</v>
       </c>
       <c r="K154" s="8">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L154" s="8" t="s">
         <v>41</v>
@@ -9296,7 +9296,7 @@
         <v>56</v>
       </c>
       <c r="K155" s="8">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="L155" s="8" t="s">
         <v>41</v>
@@ -9337,7 +9337,7 @@
         <v>60</v>
       </c>
       <c r="K156" s="8">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="L156" s="8" t="s">
         <v>41</v>
@@ -9378,7 +9378,7 @@
         <v>40</v>
       </c>
       <c r="K157" s="8">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="L157" s="8" t="s">
         <v>41</v>
@@ -9419,7 +9419,7 @@
         <v>47</v>
       </c>
       <c r="K158" s="8">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="L158" s="8" t="s">
         <v>41</v>
@@ -9460,7 +9460,7 @@
         <v>52</v>
       </c>
       <c r="K159" s="8">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="L159" s="8" t="s">
         <v>41</v>
@@ -9501,7 +9501,7 @@
         <v>56</v>
       </c>
       <c r="K160" s="8">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="L160" s="8" t="s">
         <v>41</v>
@@ -9542,7 +9542,7 @@
         <v>60</v>
       </c>
       <c r="K161" s="8">
-        <v>52</v>
+        <v>11</v>
       </c>
       <c r="L161" s="8" t="s">
         <v>41</v>
@@ -9583,7 +9583,7 @@
         <v>40</v>
       </c>
       <c r="K162" s="8">
-        <v>47</v>
+        <v>14</v>
       </c>
       <c r="L162" s="8" t="s">
         <v>41</v>
@@ -9624,7 +9624,7 @@
         <v>47</v>
       </c>
       <c r="K163" s="8">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="L163" s="8" t="s">
         <v>41</v>
@@ -9665,7 +9665,7 @@
         <v>52</v>
       </c>
       <c r="K164" s="8">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="L164" s="8" t="s">
         <v>41</v>
@@ -9706,7 +9706,7 @@
         <v>56</v>
       </c>
       <c r="K165" s="8">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="L165" s="8" t="s">
         <v>41</v>
@@ -9747,7 +9747,7 @@
         <v>60</v>
       </c>
       <c r="K166" s="8">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="L166" s="8" t="s">
         <v>41</v>
@@ -9788,7 +9788,7 @@
         <v>40</v>
       </c>
       <c r="K167" s="8">
-        <v>53</v>
+        <v>19</v>
       </c>
       <c r="L167" s="8" t="s">
         <v>41</v>
@@ -9829,7 +9829,7 @@
         <v>47</v>
       </c>
       <c r="K168" s="8">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L168" s="8" t="s">
         <v>41</v>
@@ -9870,7 +9870,7 @@
         <v>52</v>
       </c>
       <c r="K169" s="8">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="L169" s="8" t="s">
         <v>41</v>
@@ -9911,7 +9911,7 @@
         <v>56</v>
       </c>
       <c r="K170" s="8">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="L170" s="8" t="s">
         <v>41</v>
@@ -9952,7 +9952,7 @@
         <v>60</v>
       </c>
       <c r="K171" s="8">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="L171" s="8" t="s">
         <v>41</v>
@@ -9993,7 +9993,7 @@
         <v>40</v>
       </c>
       <c r="K172" s="8">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="L172" s="8" t="s">
         <v>41</v>
@@ -10034,7 +10034,7 @@
         <v>47</v>
       </c>
       <c r="K173" s="8">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="L173" s="8" t="s">
         <v>41</v>
@@ -10075,7 +10075,7 @@
         <v>52</v>
       </c>
       <c r="K174" s="8">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="L174" s="8" t="s">
         <v>41</v>
@@ -10116,7 +10116,7 @@
         <v>56</v>
       </c>
       <c r="K175" s="8">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="L175" s="8" t="s">
         <v>41</v>
@@ -10157,7 +10157,7 @@
         <v>60</v>
       </c>
       <c r="K176" s="8">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="L176" s="8" t="s">
         <v>41</v>
@@ -10198,7 +10198,7 @@
         <v>40</v>
       </c>
       <c r="K177" s="8">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="L177" s="8" t="s">
         <v>41</v>
@@ -10239,7 +10239,7 @@
         <v>47</v>
       </c>
       <c r="K178" s="8">
-        <v>19</v>
+        <v>51</v>
       </c>
       <c r="L178" s="8" t="s">
         <v>41</v>
@@ -10280,7 +10280,7 @@
         <v>52</v>
       </c>
       <c r="K179" s="8">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="L179" s="8" t="s">
         <v>41</v>
@@ -10321,7 +10321,7 @@
         <v>56</v>
       </c>
       <c r="K180" s="8">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="L180" s="8" t="s">
         <v>41</v>
@@ -10362,7 +10362,7 @@
         <v>60</v>
       </c>
       <c r="K181" s="8">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="L181" s="8" t="s">
         <v>41</v>
@@ -10403,7 +10403,7 @@
         <v>40</v>
       </c>
       <c r="K182" s="8">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="L182" s="8" t="s">
         <v>41</v>
@@ -10444,7 +10444,7 @@
         <v>47</v>
       </c>
       <c r="K183" s="8">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="L183" s="8" t="s">
         <v>41</v>
@@ -10485,7 +10485,7 @@
         <v>52</v>
       </c>
       <c r="K184" s="8">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="L184" s="8" t="s">
         <v>41</v>
@@ -10526,7 +10526,7 @@
         <v>56</v>
       </c>
       <c r="K185" s="8">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="L185" s="8" t="s">
         <v>41</v>
@@ -10567,7 +10567,7 @@
         <v>60</v>
       </c>
       <c r="K186" s="8">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="L186" s="8" t="s">
         <v>41</v>
@@ -10608,7 +10608,7 @@
         <v>40</v>
       </c>
       <c r="K187" s="8">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="L187" s="8" t="s">
         <v>41</v>
@@ -10649,7 +10649,7 @@
         <v>47</v>
       </c>
       <c r="K188" s="8">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="L188" s="8" t="s">
         <v>41</v>
@@ -10690,7 +10690,7 @@
         <v>52</v>
       </c>
       <c r="K189" s="8">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="L189" s="8" t="s">
         <v>41</v>
@@ -10731,7 +10731,7 @@
         <v>56</v>
       </c>
       <c r="K190" s="8">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="L190" s="8" t="s">
         <v>41</v>
@@ -10772,7 +10772,7 @@
         <v>60</v>
       </c>
       <c r="K191" s="8">
-        <v>57</v>
+        <v>21</v>
       </c>
       <c r="L191" s="8" t="s">
         <v>41</v>
@@ -10813,7 +10813,7 @@
         <v>40</v>
       </c>
       <c r="K192" s="8">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="L192" s="8" t="s">
         <v>41</v>
@@ -10854,7 +10854,7 @@
         <v>47</v>
       </c>
       <c r="K193" s="8">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="L193" s="8" t="s">
         <v>41</v>
@@ -10895,7 +10895,7 @@
         <v>52</v>
       </c>
       <c r="K194" s="8">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="L194" s="8" t="s">
         <v>41</v>
@@ -10936,7 +10936,7 @@
         <v>56</v>
       </c>
       <c r="K195" s="8">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="L195" s="8" t="s">
         <v>41</v>
@@ -10977,7 +10977,7 @@
         <v>60</v>
       </c>
       <c r="K196" s="8">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="L196" s="8" t="s">
         <v>41</v>
@@ -11018,7 +11018,7 @@
         <v>40</v>
       </c>
       <c r="K197" s="8">
-        <v>12</v>
+        <v>58</v>
       </c>
       <c r="L197" s="8" t="s">
         <v>41</v>
@@ -11059,7 +11059,7 @@
         <v>47</v>
       </c>
       <c r="K198" s="8">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="L198" s="8" t="s">
         <v>41</v>
@@ -11100,7 +11100,7 @@
         <v>52</v>
       </c>
       <c r="K199" s="8">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="L199" s="8" t="s">
         <v>41</v>
@@ -11141,7 +11141,7 @@
         <v>56</v>
       </c>
       <c r="K200" s="8">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="L200" s="8" t="s">
         <v>41</v>
@@ -11182,7 +11182,7 @@
         <v>60</v>
       </c>
       <c r="K201" s="8">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="L201" s="8" t="s">
         <v>41</v>
@@ -11223,7 +11223,7 @@
         <v>40</v>
       </c>
       <c r="K202" s="8">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="L202" s="8" t="s">
         <v>41</v>
@@ -11264,7 +11264,7 @@
         <v>47</v>
       </c>
       <c r="K203" s="8">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="L203" s="8" t="s">
         <v>41</v>
@@ -11305,7 +11305,7 @@
         <v>52</v>
       </c>
       <c r="K204" s="8">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="L204" s="8" t="s">
         <v>41</v>
@@ -11346,7 +11346,7 @@
         <v>56</v>
       </c>
       <c r="K205" s="8">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="L205" s="8" t="s">
         <v>41</v>
@@ -11387,7 +11387,7 @@
         <v>60</v>
       </c>
       <c r="K206" s="8">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="L206" s="8" t="s">
         <v>41</v>
@@ -11428,7 +11428,7 @@
         <v>40</v>
       </c>
       <c r="K207" s="8">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="L207" s="8" t="s">
         <v>41</v>
@@ -11469,7 +11469,7 @@
         <v>47</v>
       </c>
       <c r="K208" s="8">
-        <v>56</v>
+        <v>11</v>
       </c>
       <c r="L208" s="8" t="s">
         <v>41</v>
@@ -11510,7 +11510,7 @@
         <v>52</v>
       </c>
       <c r="K209" s="8">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="L209" s="8" t="s">
         <v>41</v>
@@ -11551,7 +11551,7 @@
         <v>56</v>
       </c>
       <c r="K210" s="8">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="L210" s="8" t="s">
         <v>41</v>
@@ -11592,7 +11592,7 @@
         <v>60</v>
       </c>
       <c r="K211" s="8">
-        <v>11</v>
+        <v>52</v>
       </c>
       <c r="L211" s="8" t="s">
         <v>41</v>
@@ -11633,7 +11633,7 @@
         <v>40</v>
       </c>
       <c r="K212" s="8">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="L212" s="8" t="s">
         <v>41</v>
@@ -11674,7 +11674,7 @@
         <v>47</v>
       </c>
       <c r="K213" s="8">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="L213" s="8" t="s">
         <v>41</v>
@@ -11715,7 +11715,7 @@
         <v>52</v>
       </c>
       <c r="K214" s="8">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="L214" s="8" t="s">
         <v>41</v>
@@ -11756,7 +11756,7 @@
         <v>56</v>
       </c>
       <c r="K215" s="8">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="L215" s="8" t="s">
         <v>41</v>
@@ -11797,7 +11797,7 @@
         <v>60</v>
       </c>
       <c r="K216" s="8">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="L216" s="8" t="s">
         <v>41</v>
@@ -11838,7 +11838,7 @@
         <v>40</v>
       </c>
       <c r="K217" s="8">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="L217" s="8" t="s">
         <v>41</v>
@@ -11879,7 +11879,7 @@
         <v>47</v>
       </c>
       <c r="K218" s="8">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="L218" s="8" t="s">
         <v>41</v>
@@ -11920,7 +11920,7 @@
         <v>52</v>
       </c>
       <c r="K219" s="8">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="L219" s="8" t="s">
         <v>41</v>
@@ -11961,7 +11961,7 @@
         <v>56</v>
       </c>
       <c r="K220" s="8">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="L220" s="8" t="s">
         <v>41</v>
@@ -12002,7 +12002,7 @@
         <v>60</v>
       </c>
       <c r="K221" s="8">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="L221" s="8" t="s">
         <v>41</v>
@@ -12043,7 +12043,7 @@
         <v>40</v>
       </c>
       <c r="K222" s="8">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="L222" s="8" t="s">
         <v>41</v>
@@ -12084,7 +12084,7 @@
         <v>47</v>
       </c>
       <c r="K223" s="8">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="L223" s="8" t="s">
         <v>41</v>
@@ -12125,7 +12125,7 @@
         <v>52</v>
       </c>
       <c r="K224" s="8">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="L224" s="8" t="s">
         <v>41</v>
@@ -12166,7 +12166,7 @@
         <v>56</v>
       </c>
       <c r="K225" s="8">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="L225" s="8" t="s">
         <v>41</v>
@@ -12207,7 +12207,7 @@
         <v>60</v>
       </c>
       <c r="K226" s="8">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="L226" s="8" t="s">
         <v>41</v>
@@ -12248,7 +12248,7 @@
         <v>40</v>
       </c>
       <c r="K227" s="8">
-        <v>22</v>
+        <v>52</v>
       </c>
       <c r="L227" s="8" t="s">
         <v>41</v>
@@ -12289,7 +12289,7 @@
         <v>47</v>
       </c>
       <c r="K228" s="8">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="L228" s="8" t="s">
         <v>41</v>
@@ -12330,7 +12330,7 @@
         <v>52</v>
       </c>
       <c r="K229" s="8">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="L229" s="8" t="s">
         <v>41</v>
@@ -12371,7 +12371,7 @@
         <v>56</v>
       </c>
       <c r="K230" s="8">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="L230" s="8" t="s">
         <v>41</v>
@@ -12412,7 +12412,7 @@
         <v>60</v>
       </c>
       <c r="K231" s="8">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="L231" s="8" t="s">
         <v>41</v>
@@ -12453,7 +12453,7 @@
         <v>40</v>
       </c>
       <c r="K232" s="8">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="L232" s="8" t="s">
         <v>41</v>
@@ -12535,7 +12535,7 @@
         <v>52</v>
       </c>
       <c r="K234" s="8">
-        <v>14</v>
+        <v>49</v>
       </c>
       <c r="L234" s="8" t="s">
         <v>41</v>
@@ -12576,7 +12576,7 @@
         <v>56</v>
       </c>
       <c r="K235" s="8">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="L235" s="8" t="s">
         <v>41</v>
@@ -12617,7 +12617,7 @@
         <v>60</v>
       </c>
       <c r="K236" s="8">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="L236" s="8" t="s">
         <v>41</v>
@@ -12658,7 +12658,7 @@
         <v>40</v>
       </c>
       <c r="K237" s="8">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="L237" s="8" t="s">
         <v>41</v>
@@ -12699,7 +12699,7 @@
         <v>47</v>
       </c>
       <c r="K238" s="8">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="L238" s="8" t="s">
         <v>41</v>
@@ -12740,7 +12740,7 @@
         <v>52</v>
       </c>
       <c r="K239" s="8">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="L239" s="8" t="s">
         <v>41</v>
@@ -12781,7 +12781,7 @@
         <v>56</v>
       </c>
       <c r="K240" s="8">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="L240" s="8" t="s">
         <v>41</v>
@@ -12822,7 +12822,7 @@
         <v>60</v>
       </c>
       <c r="K241" s="8">
-        <v>22</v>
+        <v>59</v>
       </c>
       <c r="L241" s="8" t="s">
         <v>41</v>
